--- a/artfynd/A 6934-2026 artfynd.xlsx
+++ b/artfynd/A 6934-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -804,6 +804,444 @@
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>131600741</v>
+      </c>
+      <c r="B3" t="n">
+        <v>79258</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Långåkervallen, Långåkervallen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>411575</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7019788</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Undersåker</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Fabian Pettersson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Fabian Pettersson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>131594488</v>
+      </c>
+      <c r="B4" t="n">
+        <v>91846</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Långåkervallen, Långåkervallen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>411583</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7019760</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Undersåker</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Fabian Pettersson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Fabian Pettersson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>131600559</v>
+      </c>
+      <c r="B5" t="n">
+        <v>91846</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Långåkervallen, Långåkervallen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>411547</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7019798</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Undersåker</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>12:36</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>12:36</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Fabian Pettersson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Fabian Pettersson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>131597386</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58055</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Långåkervallen, Långåkervallen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>411540</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7019763</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Undersåker</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>11:44</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>11:44</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Fabian Pettersson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Fabian Pettersson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 6934-2026 artfynd.xlsx
+++ b/artfynd/A 6934-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>106908236</v>
+        <v>106890604</v>
       </c>
       <c r="B2" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>411662.956300929</v>
+        <v>411630</v>
       </c>
       <c r="R2" t="n">
-        <v>7019938.828913112</v>
+        <v>7019739</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -775,21 +770,6 @@
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -809,11 +789,11 @@
         <v>131600741</v>
       </c>
       <c r="B3" t="n">
-        <v>79276</v>
+        <v>79373</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -917,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131594488</v>
+        <v>131597386</v>
       </c>
       <c r="B4" t="n">
-        <v>91868</v>
+        <v>58136</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -928,30 +908,48 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Långåkervallen, Långåkervallen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>411583</v>
+        <v>411540</v>
       </c>
       <c r="R4" t="n">
-        <v>7019760</v>
+        <v>7019763</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -983,7 +981,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,7 +991,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1017,230 +1015,6 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>131600559</v>
-      </c>
-      <c r="B5" t="n">
-        <v>91868</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Långåkervallen, Långåkervallen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q5" t="n">
-        <v>411547</v>
-      </c>
-      <c r="R5" t="n">
-        <v>7019798</v>
-      </c>
-      <c r="S5" t="n">
-        <v>10</v>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>Undersåker</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>12:36</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>12:36</t>
-        </is>
-      </c>
-      <c r="AD5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT5" t="inlineStr"/>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>Fabian Pettersson</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>Fabian Pettersson</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>131597386</v>
-      </c>
-      <c r="B6" t="n">
-        <v>58073</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>103021</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Talltita</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Poecile montanus</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Långåkervallen, Långåkervallen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q6" t="n">
-        <v>411540</v>
-      </c>
-      <c r="R6" t="n">
-        <v>7019763</v>
-      </c>
-      <c r="S6" t="n">
-        <v>10</v>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>Undersåker</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>11:44</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>11:44</t>
-        </is>
-      </c>
-      <c r="AD6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT6" t="inlineStr"/>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>Fabian Pettersson</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>Fabian Pettersson</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
